--- a/01 - Mis finanzas (Argentina).xlsx
+++ b/01 - Mis finanzas (Argentina).xlsx
@@ -716,7 +716,7 @@
     <row r="14" ht="30" customHeight="1" s="27">
       <c r="B14" s="33" t="inlineStr">
         <is>
-          <t>Si te sirvió y querés colaborar, mi alias de Mercado Pago es igna.pelliza. Gracias.</t>
+          <t>¡Gracias! Si te sirvió y querés colaborar, mi alias de Mercado Pago es:  igna.pelliza</t>
         </is>
       </c>
     </row>
